--- a/output/stock_quant_scores/KMI_income_df.xlsx
+++ b/output/stock_quant_scores/KMI_income_df.xlsx
@@ -1286,7 +1286,9 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>4540000000</v>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1295,11 +1297,15 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>0.78</v>
+      </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>1784000000</v>
+      </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
@@ -1332,9 +1338,13 @@
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
+      <c r="AU6" t="n">
+        <v>7982000000</v>
+      </c>
       <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
+      <c r="AW6" t="n">
+        <v>16610000000</v>
+      </c>
       <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
